--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/aae/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>426</v>
